--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.650309003668395</v>
+        <v>1.405675213096114</v>
       </c>
       <c r="D2" t="n">
-        <v>8.558794463737588</v>
+        <v>1.390804100357358</v>
       </c>
       <c r="E2" t="n">
-        <v>5.229707159128757</v>
+        <v>0.849827413358423</v>
       </c>
       <c r="F2" t="n">
-        <v>2.265010755321801</v>
+        <v>0.3680642477397926</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.10972332192591</v>
+        <v>3.10533003981296</v>
       </c>
       <c r="D3" t="n">
-        <v>13.08881597438119</v>
+        <v>2.126932595836943</v>
       </c>
       <c r="E3" t="n">
-        <v>5.229707159128757</v>
+        <v>0.849827413358423</v>
       </c>
       <c r="F3" t="n">
-        <v>2.265010755321801</v>
+        <v>0.3680642477397926</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
